--- a/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
@@ -625,36 +625,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">317
-</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
@@ -664,7 +639,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -676,71 +651,46 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="inlineStr">
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">45
 </t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
       <c r="X4" s="2" t="n"/>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
@@ -757,70 +707,45 @@
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12620
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -828,42 +753,34 @@
 </t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">927
-</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
+      <c r="T5" s="2" t="n"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="n"/>
+          <t xml:space="preserve">2929
+</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">68
@@ -883,131 +800,120 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">916
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="n"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">507
-</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="n"/>
+          <t xml:space="preserve">7072
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">742
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="n"/>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n"/>
@@ -1023,95 +929,100 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">316
+</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1123,32 +1034,31 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n"/>
@@ -1167,121 +1077,118 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="n"/>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1301,126 +1208,113 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">43
+</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
-</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">488
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3822
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n"/>
@@ -1439,122 +1333,122 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1424
+</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
-</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15912
-</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="n"/>
+          <t xml:space="preserve">458
+</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1223
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">386
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1574,65 +1468,64 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+          <t xml:space="preserve">437
+</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1641,55 +1534,50 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">3188
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1709,119 +1597,121 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1122
+577
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">62
+</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">612
+</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1841,122 +1731,119 @@
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">183
 </t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="n"/>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">2627
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="n"/>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1976,37 +1863,37 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">2824
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2018,31 +1905,31 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9043
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2054,55 +1941,51 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1252
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Z14" s="2" t="n"/>
@@ -2121,36 +2004,37 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">983
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2162,81 +2046,80 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2152
+</t>
+        </is>
+      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2256,124 +2139,117 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9532
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">922
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18417
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -2393,113 +2269,132 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2429
+</t>
+        </is>
+      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8083
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2519,122 +2414,108 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">953
+</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2456
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4921
+</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2518
-</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">649
-</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="n"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2654,125 +2535,122 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262622
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9812
-</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
+          <t xml:space="preserve">8282
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z19" s="2" t="n"/>
@@ -2791,127 +2669,128 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">857
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2931,127 +2810,123 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12922
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1280
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9272
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="n"/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3071,133 +2946,125 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>381</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1842
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1999
-</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1210
-</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1084
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="n"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3217,131 +3084,116 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">3894
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1851
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13932
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>412</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5360
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
-</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="n"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4278
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z23" s="2" t="n"/>
@@ -3360,126 +3212,129 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32828
+</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
+</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">939
+</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">802
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="n"/>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3496,125 +3351,129 @@
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1446
+</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4978
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0926
+</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5922
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">22 1
 </t>
         </is>
       </c>
@@ -3634,123 +3493,121 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">632
-</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
@@ -3769,126 +3626,128 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">938
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2393
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2349
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t xml:space="preserve">62
+</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="Z27" s="2" t="n"/>
@@ -3907,131 +3766,128 @@
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19584
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8539
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="Z28" s="2" t="n"/>
@@ -4050,13 +3906,13 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1539
 </t>
         </is>
       </c>
@@ -4068,109 +3924,115 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26511
+          <t xml:space="preserve">16825
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1902
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
-</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">64
+</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1042
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="2" t="n"/>
@@ -4189,119 +4051,116 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">3061
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">39086
+</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>264</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
-</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="n"/>
+          <t xml:space="preserve">3222
+</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492
+</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1346
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">10426
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">3225
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4321,114 +4180,118 @@
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27511
+</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="n"/>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4526
+</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>226444</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="n"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
@@ -4448,73 +4311,80 @@
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t xml:space="preserve">47
+</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2829
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4526,37 +4396,37 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -4576,93 +4446,91 @@
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139326
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
-</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1879
+</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
-</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n"/>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
@@ -4674,25 +4542,25 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4712,93 +4580,102 @@
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9282
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
@@ -4810,25 +4687,25 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -4848,123 +4725,116 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
-</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n"/>
+          <t xml:space="preserve">7922
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>801</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -4981,68 +4851,80 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180902
-</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">10
@@ -5057,51 +4939,47 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1306
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t xml:space="preserve">2973
+</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">372
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">582
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
       <c r="Z36" s="2" t="n"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5118,64 +4996,66 @@
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>846344</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14418
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09502
+          <t xml:space="preserve">94503
 </t>
         </is>
       </c>
@@ -5188,54 +5068,56 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">12421
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">2672
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">324
+</t>
         </is>
       </c>
       <c r="Z37" s="2" t="n"/>
@@ -5254,60 +5136,60 @@
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t xml:space="preserve">1615
+</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>883384</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7857
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -5325,7 +5207,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5333,38 +5215,37 @@
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2852
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z38" s="2" t="n"/>
@@ -5383,51 +5264,59 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">612
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="M39" s="2" t="n"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -5440,13 +5329,13 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5458,7 +5347,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5470,25 +5359,25 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5508,128 +5397,117 @@
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">2478
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5646,52 +5524,57 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5704,32 +5587,32 @@
       <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5741,25 +5624,25 @@
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -5785,55 +5668,55 @@
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">941
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -5845,56 +5728,76 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19221
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="n"/>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="n"/>
-      <c r="W42" s="2" t="n"/>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="n"/>
+          <t xml:space="preserve">5822
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
@@ -5908,67 +5811,99 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+745
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">3
+6
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3819
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5979,25 +5914,25 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9272
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Z43" s="2" t="n"/>
@@ -6016,47 +5951,51 @@
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">4262
+7
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">2429
+14
+</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">7
+7
 </t>
         </is>
       </c>
@@ -6064,45 +6003,44 @@
       <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13663
+          <t xml:space="preserve">77 777
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21213
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="n"/>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6114,14 +6052,13 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">3272
 </t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>504</t>
         </is>
       </c>
       <c r="Z44" s="2" t="n"/>
@@ -6140,7 +6077,7 @@
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -6152,29 +6089,39 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="n"/>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2828
+</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">184
@@ -6187,29 +6134,35 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">983
-</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="Q45" s="2" t="n"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -6224,7 +6177,7 @@
       <c r="W45" s="2" t="n"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 2
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
@@ -6242,74 +6195,104 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">323
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">062
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="n"/>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">8
 </t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="n"/>
+      <c r="T46" s="2" t="n"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12901
+</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
+          <t xml:space="preserve">1999
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501
-</t>
-        </is>
-      </c>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6321,6 +6304,20 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+1212
+</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
@@ -625,11 +625,36 @@
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
@@ -639,7 +664,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1829
 </t>
         </is>
       </c>
@@ -651,44 +676,68 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
-      <c r="W4" s="2" t="n"/>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
@@ -707,87 +756,129 @@
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
+          <t xml:space="preserve">2176
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1239
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="n"/>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2929
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="n"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="n"/>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
@@ -803,120 +894,132 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">0170
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">916
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n"/>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2074
+</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">1144
+</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="n"/>
+          <t xml:space="preserve">2513
+</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="n"/>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -929,136 +1032,126 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">2105
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n"/>
@@ -1077,119 +1170,123 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2946
+</t>
+        </is>
+      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n"/>
@@ -1208,112 +1305,122 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1125
+</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">9578
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">9492
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14546
+</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n"/>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11109
+</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="n"/>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3186
+</t>
+        </is>
+      </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1269
+</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="n"/>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">2311
 </t>
         </is>
       </c>
@@ -1333,126 +1440,126 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">972
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">458
-</t>
-        </is>
-      </c>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">912
+</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n"/>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n"/>
+          <t xml:space="preserve">2162
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1468,119 +1575,118 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="n"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3188
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1268
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1597,121 +1703,121 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="n"/>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1945
 </t>
         </is>
       </c>
@@ -1731,119 +1837,116 @@
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">104
+</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2627
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -1863,128 +1966,126 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1495
+</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165
+</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>43414</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29234
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">582
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1252
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">264
 </t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2824
-</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1929
-</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2004,55 +2105,48 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">983
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2062,64 +2156,70 @@
 </t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="n"/>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2152
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -2139,117 +2239,124 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n"/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">11823
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="n"/>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19492
+</t>
+        </is>
+      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">17088
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -2269,132 +2376,113 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">4129
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">649
+</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="n"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1466
-</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">853
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2414,108 +2502,120 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>466</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2456
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">4110
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2288
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1072
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">260
+</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4921
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2535,121 +2635,111 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">29505
+</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262622
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n"/>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8282
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2669,128 +2759,114 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>486</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">262
+</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -2810,123 +2886,122 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9272
-</t>
-        </is>
-      </c>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="n"/>
+          <t xml:space="preserve">1191
+</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2946,125 +3021,128 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t xml:space="preserve">298
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">2399
+</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="n"/>
+          <t xml:space="preserve">9562
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1399
+</t>
+        </is>
+      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1947
 </t>
         </is>
       </c>
@@ -3084,116 +3162,117 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">11441
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">2904
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3894
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">024644
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13932
-</t>
-        </is>
-      </c>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14209
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n"/>
+          <t xml:space="preserve">9316
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">11210
+</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1072
+</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="n"/>
+          <t xml:space="preserve">93606
+</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11084
+</t>
+        </is>
+      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">09278
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Z23" s="2" t="n"/>
@@ -3212,129 +3291,115 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">18298
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32828
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">939
-</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
+          <t>13164</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t xml:space="preserve">1239
+</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">7282
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="Z24" s="2" t="n"/>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3351,129 +3416,127 @@
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4978
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">11922
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1090
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0926
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1692
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 1
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3493,120 +3556,122 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t xml:space="preserve">296
+</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1592
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">7162
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3626,68 +3691,68 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,55 +3763,50 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="n"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1802
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3766,127 +3826,126 @@
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1687
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1190809
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8539
+          <t xml:space="preserve">402
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">5622
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t xml:space="preserve">538
+</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3906,13 +3965,13 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -3924,67 +3983,62 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1892
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16825
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1958
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -3996,25 +4050,25 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1394
 </t>
         </is>
       </c>
@@ -4026,13 +4080,14 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="Z29" s="2" t="n"/>
@@ -4051,116 +4106,122 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3061
+          <t xml:space="preserve">194984
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39086
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">313
+</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2927
+</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr"/>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3222
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11123
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1538222
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10426
+          <t xml:space="preserve">11042
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3225
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">9284
 </t>
         </is>
       </c>
@@ -4180,118 +4241,116 @@
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27511
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4526
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1826
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">253
 </t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="n"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">642
+</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4311,125 +4370,124 @@
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">14183
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12196
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2829
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="n"/>
       <c r="Z32" s="2" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4446,68 +4504,70 @@
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">945
+</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1879
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4518,49 +4578,49 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">1803
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
@@ -4580,79 +4640,64 @@
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">12825
 </t>
         </is>
       </c>
@@ -4664,48 +4709,48 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">1863
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -4725,116 +4770,123 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7922
-</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="n"/>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">8320
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -4851,135 +4903,129 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
+      <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1514
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">12312
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2973
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">3852
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
       <c r="Z36" s="2" t="n"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4996,127 +5042,127 @@
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">11615
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">87110
+</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">9811
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94503
-</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="n"/>
+          <t xml:space="preserve">9410
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9506
+</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1428
 </t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">2413
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12421
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2672
+          <t xml:space="preserve">3672
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5136,110 +5182,115 @@
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">2515
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">941
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7857
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="n"/>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">12749
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5264,45 +5315,50 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">024516
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">1791
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -5311,32 +5367,31 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -5347,37 +5402,36 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">19482
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -5397,117 +5451,127 @@
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">018
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1910
+</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="n"/>
+          <t xml:space="preserve">1070
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">923
+</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">2998
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">270
+</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2478
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5524,125 +5588,125 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
+      <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">2324
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">10856
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">10820
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5668,133 +5732,121 @@
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">11229
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">11020
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">544
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2662
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="n"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2492
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">12221
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">9603
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5822
+          <t xml:space="preserve">102712
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2167
 </t>
         </is>
       </c>
@@ -5812,129 +5864,28 @@
         </is>
       </c>
       <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">324
-</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1285
-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-745
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
-      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+      <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-6
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">953
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
+      <c r="V43" s="2" t="n"/>
+      <c r="W43" s="2" t="n"/>
+      <c r="X43" s="2" t="n"/>
+      <c r="Y43" s="2" t="n"/>
       <c r="Z43" s="2" t="n"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5949,118 +5900,28 @@
         </is>
       </c>
       <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-14
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
-      </c>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
-      </c>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2418
-</t>
-        </is>
-      </c>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="n"/>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3272
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="n"/>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6077,7 +5938,7 @@
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
@@ -6089,99 +5950,107 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2828
-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1909
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="n"/>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="n"/>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
       <c r="Z45" s="2" t="n"/>
       <c r="AA45" t="inlineStr">
         <is>
@@ -6197,102 +6066,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 191
-</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
-      </c>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="n"/>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12901
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1999
-</t>
-        </is>
-      </c>
+      <c r="U46" s="2" t="n"/>
+      <c r="V46" s="2" t="n"/>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="n"/>
+          <t xml:space="preserve">92110
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198855
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165608
+</t>
+        </is>
+      </c>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6304,20 +6118,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-1212
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
@@ -624,7 +624,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">917
@@ -639,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
@@ -651,7 +651,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -661,10 +661,15 @@
 </t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -676,19 +681,19 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -700,7 +705,8 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t xml:space="preserve">306
+</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -711,13 +717,14 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t xml:space="preserve">452
+</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -753,16 +760,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -774,19 +781,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -804,13 +811,13 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">7146
 </t>
         </is>
       </c>
@@ -822,17 +829,19 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">994
+</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -844,7 +853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -854,29 +863,40 @@
 </t>
         </is>
       </c>
-      <c r="U5" s="2" t="n"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="n"/>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -894,25 +914,25 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -922,7 +942,12 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">44
@@ -931,74 +956,79 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2074
-</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2513
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
@@ -1014,12 +1044,7 @@
 </t>
         </is>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
+      <c r="Z6" s="2" t="n"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1035,7 +1060,7 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2105
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -1047,7 +1072,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1059,7 +1084,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1798
 </t>
         </is>
       </c>
@@ -1083,21 +1108,27 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>013</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1114,22 +1145,17 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -1144,7 +1170,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1167,7 +1193,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1176,13 +1202,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1200,18 +1226,20 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1229,13 +1257,14 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">080
+</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1246,7 +1275,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1258,7 +1287,8 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t xml:space="preserve">662
+</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,7 +1299,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1281,15 +1311,22 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="n"/>
+          <t xml:space="preserve">592
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1302,7 +1339,7 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1474
@@ -1311,43 +1348,43 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9578
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
@@ -1363,10 +1400,15 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1001
+</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14546
+          <t xml:space="preserve">4516
 </t>
         </is>
       </c>
@@ -1384,13 +1426,14 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11109
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1401,27 +1444,31 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n"/>
@@ -1437,7 +1484,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1446,23 +1493,28 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n"/>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -1471,11 +1523,11 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
+          <t xml:space="preserve">08604
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">185
@@ -1484,10 +1536,16 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -1496,8 +1554,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1520,13 +1577,13 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1538,25 +1595,25 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1572,7 +1629,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">290
@@ -1581,38 +1638,44 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1623,16 +1686,22 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">1183
+</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -1641,52 +1710,58 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">2398
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
       <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1700,7 +1775,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -1709,7 +1789,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -1721,13 +1801,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -1739,76 +1819,88 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672
+</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1612
-</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -1817,11 +1909,16 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1945
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1645
+</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>7</t>
@@ -1843,45 +1940,61 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="n"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -1893,19 +2006,20 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1922,7 +2036,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1940,17 +2054,22 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="n"/>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -1963,7 +2082,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 3 3 1
+</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -1978,13 +2102,13 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1495
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2008,54 +2132,61 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29234
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -2067,7 +2198,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">2151
 </t>
         </is>
       </c>
@@ -2085,11 +2216,16 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9514
+</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>9</t>
@@ -2102,22 +2238,23 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">28919
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2128,20 +2265,26 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2152,26 +2295,31 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2183,47 +2331,52 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2095
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="n"/>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -2236,7 +2389,7 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1408
@@ -2257,12 +2410,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">481
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2274,14 +2428,20 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">9513
+</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2292,29 +2452,31 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t xml:space="preserve">94552
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11823
+          <t xml:space="preserve">11829
 </t>
         </is>
       </c>
@@ -2326,37 +2488,32 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">213142
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11585
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17088
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112746
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1005
 </t>
         </is>
       </c>
@@ -2373,88 +2530,103 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2518
+</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">233
 </t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4129
-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">649
@@ -2469,14 +2641,19 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">222 3
+</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2499,15 +2676,16 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">3089
+</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2525,18 +2703,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2548,33 +2727,39 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2585,31 +2770,31 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2632,10 +2817,10 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29505
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
@@ -2659,34 +2844,50 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
+          <t xml:space="preserve">14183
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2697,49 +2898,49 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2756,10 +2957,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">2853
+</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2776,13 +2983,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2793,33 +3001,44 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2837,36 +3056,37 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2883,10 +3103,10 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2898,19 +3118,19 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2928,26 +3148,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2959,7 +3185,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2971,19 +3197,19 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2993,15 +3219,10 @@
 </t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
+      <c r="X21" s="2" t="n"/>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3018,22 +3239,22 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3045,19 +3266,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3069,26 +3290,31 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n"/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3100,7 +3326,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3112,28 +3338,28 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9562
+          <t xml:space="preserve">8562
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">802
@@ -3142,7 +3368,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1947
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
@@ -3159,33 +3385,48 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11441
+          <t xml:space="preserve">19446
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2904
+          <t xml:space="preserve">9104
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2208
+</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
+</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -3194,25 +3435,26 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024644
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">939
+</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316
+          <t xml:space="preserve">9312
 </t>
         </is>
       </c>
@@ -3224,7 +3466,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -3236,36 +3478,37 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93606
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11084
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09278
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -3288,28 +3531,28 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18298
+          <t xml:space="preserve">8228
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1914
 </t>
         </is>
       </c>
@@ -3321,12 +3564,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10589
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">988
@@ -3335,14 +3583,20 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t xml:space="preserve">2186
+</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 312
+</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3354,19 +3608,19 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3378,22 +3632,17 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2817
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
+      <c r="X24" s="2" t="n"/>
       <c r="Y24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">25
@@ -3413,7 +3662,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">298
@@ -3422,7 +3671,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3440,13 +3689,13 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -3458,35 +3707,35 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11922
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1090
-</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -3495,7 +3744,8 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3506,37 +3756,37 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1692
+          <t xml:space="preserve">1678
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">591
 </t>
         </is>
       </c>
@@ -3553,16 +3803,16 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3586,7 +3836,8 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3597,27 +3848,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
+          <t xml:space="preserve">1926
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 18
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">7 91
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3629,19 +3890,18 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3665,7 +3925,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -3688,7 +3948,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">273
@@ -3697,7 +3962,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -3715,7 +3980,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3733,7 +3998,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3745,14 +4010,20 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n"/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3769,7 +4040,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3781,32 +4052,32 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">632
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">109
 </t>
         </is>
       </c>
-      <c r="U27" s="2" t="n"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="n"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3823,16 +4094,16 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3844,19 +4115,19 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3868,31 +4139,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n"/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190809
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -3904,13 +4181,14 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t xml:space="preserve">2740
+</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3921,31 +4199,31 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5622
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3962,7 +4240,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">301
@@ -3971,68 +4249,72 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1918
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1892
-</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1958
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="n"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4062,31 +4344,31 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1394
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4103,10 +4385,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194984
+          <t xml:space="preserve">19484
 </t>
         </is>
       </c>
@@ -4136,92 +4423,98 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2927
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">9207
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11123
-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="n"/>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538222
+          <t xml:space="preserve">33222
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">10881
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11042
+          <t xml:space="preserve">11841
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9284
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -4238,16 +4531,16 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">2397
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4259,7 +4552,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -4271,23 +4564,35 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -4296,61 +4601,61 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">773
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4367,33 +4672,35 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1118
+</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4404,7 +4711,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4426,10 +4733,15 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12196
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4447,7 +4759,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4459,31 +4771,31 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">2881
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">4155
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -4501,7 +4813,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">326
@@ -4510,19 +4827,19 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4534,33 +4851,43 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -4590,37 +4917,37 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">1658
 </t>
         </is>
       </c>
@@ -4637,10 +4964,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -4652,7 +4984,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2418
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4670,19 +5002,19 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -4692,18 +5024,33 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1511
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12825
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -4721,13 +5068,14 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4738,19 +5086,19 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4770,31 +5118,30 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4822,14 +5169,19 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -4856,19 +5208,19 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8320
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -4880,13 +5232,13 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
@@ -4903,10 +5255,10 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">336
 </t>
         </is>
       </c>
@@ -4930,19 +5282,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1514
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -4958,29 +5310,34 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -4998,7 +5355,7 @@
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5016,13 +5373,13 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3852
+          <t xml:space="preserve">557
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5039,7 +5396,7 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">11615
@@ -5048,7 +5405,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -5060,46 +5417,52 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87110
+          <t xml:space="preserve">8180
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">0117
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n"/>
+          <t xml:space="preserve">7210
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">9506
@@ -5108,7 +5471,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -5120,34 +5483,34 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1206
+</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1110
 </t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2413
-</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1009
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1299
@@ -5156,13 +5519,13 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3672
+          <t xml:space="preserve">36722
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">5372
 </t>
         </is>
       </c>
@@ -5179,10 +5542,11 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5193,7 +5557,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515
+          <t xml:space="preserve">25246
 </t>
         </is>
       </c>
@@ -5205,44 +5569,50 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n"/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5260,25 +5630,25 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12749
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5296,7 +5666,8 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="2" t="n"/>
@@ -5315,72 +5686,75 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024516
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1791
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5391,7 +5765,8 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t xml:space="preserve">1426
+</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -5402,13 +5777,14 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19482
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -5425,16 +5801,11 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="n"/>
       <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5448,70 +5819,76 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1070
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5118
+</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5523,31 +5900,31 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2998
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2608
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">1926
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -5559,13 +5936,13 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">2518
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -5588,22 +5965,22 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324
+          <t xml:space="preserve">9218
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10856
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5615,44 +5992,39 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
+          <t xml:space="preserve">2049
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -5664,25 +6036,25 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10820
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5700,13 +6072,13 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5729,127 +6101,114 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11229
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11020
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">544
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">19502
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="n"/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="n"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12221
-</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9603
-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102712
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="n"/>
+      <c r="W42" s="2" t="n"/>
+      <c r="X42" s="2" t="n"/>
+      <c r="Y42" s="2" t="n"/>
       <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
@@ -5863,7 +6222,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
@@ -5899,7 +6263,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -5938,116 +6307,128 @@
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">2412
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">5097
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">8187
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">9663
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">02712
+</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -6064,46 +6445,121 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">937
+</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="n"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92110
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198855
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165608
+          <t xml:space="preserve">12111011
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -639,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -651,7 +651,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -687,13 +687,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -717,14 +716,13 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
-</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -735,7 +733,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -760,7 +758,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">252
@@ -775,7 +778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -787,25 +790,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -817,19 +819,19 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">994
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -853,7 +855,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -865,19 +867,19 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">2439
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -914,121 +916,121 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">272
 </t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">975
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -1040,7 +1042,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1127,13 +1129,13 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">4201
 </t>
         </is>
       </c>
@@ -1145,17 +1147,22 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -1170,7 +1177,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -1193,7 +1200,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1208,7 +1220,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1226,13 +1238,13 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1287,7 +1299,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1299,7 +1311,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1317,13 +1329,13 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1348,7 +1360,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
@@ -1360,7 +1372,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
@@ -1378,28 +1390,28 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">9441
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">926
 </t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1001
@@ -1408,8 +1420,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
-</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1432,7 +1443,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -1444,13 +1455,13 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1468,7 +1479,8 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n"/>
@@ -1484,7 +1496,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1505,13 +1522,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1916
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1523,11 +1540,16 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08604
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">185
@@ -1542,7 +1564,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1583,7 +1605,7 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1613,7 +1635,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -1656,13 +1678,13 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -1674,14 +1696,13 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1692,16 +1713,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -1716,31 +1732,31 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2398
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1752,7 +1768,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1777,7 +1793,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1789,7 +1805,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1801,13 +1817,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -1825,7 +1841,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
@@ -1843,7 +1859,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1861,7 +1877,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -1873,19 +1889,19 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1897,7 +1913,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -1909,13 +1925,13 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -1946,7 +1962,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1958,7 +1974,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -1970,7 +1986,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1994,7 +2010,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2012,7 +2028,7 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -2036,7 +2052,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -2082,12 +2098,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 3 3 1
-</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2102,7 +2113,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2114,7 +2125,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -2144,19 +2155,14 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -2168,7 +2174,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -2180,13 +2186,13 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -2198,7 +2204,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
@@ -2216,13 +2222,13 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">7172
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9514
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2238,16 +2244,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28919
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2271,19 +2282,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2295,25 +2306,25 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
@@ -2331,7 +2342,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -2355,7 +2366,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2373,7 +2384,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2392,19 +2403,18 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">19404
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -2416,7 +2426,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">015
 </t>
         </is>
       </c>
@@ -2428,13 +2438,13 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -2458,7 +2468,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94552
+          <t xml:space="preserve">4532
 </t>
         </is>
       </c>
@@ -2470,13 +2480,13 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11829
+          <t xml:space="preserve">11273
 </t>
         </is>
       </c>
@@ -2488,32 +2498,32 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213142
+          <t xml:space="preserve">0182
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11585
+          <t xml:space="preserve">9848
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112746
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1005
+          <t xml:space="preserve">100646
 </t>
         </is>
       </c>
@@ -2530,15 +2540,10 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2550,7 +2555,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2574,7 +2579,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -2587,16 +2592,11 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">91
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2617,19 +2617,19 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2353
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222 3
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2679,37 +2679,36 @@
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3089
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2727,13 +2726,13 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2752,8 +2751,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2770,13 +2768,13 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2788,7 +2786,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2817,10 +2815,15 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -2844,7 +2847,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>469</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2867,7 +2870,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2904,19 +2907,19 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2957,21 +2960,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3019,11 +3017,16 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">902
@@ -3050,25 +3053,25 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -3080,7 +3083,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3106,8 +3109,7 @@
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3124,22 +3126,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -3148,7 +3150,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -3179,13 +3181,13 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3197,13 +3199,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -3242,8 +3244,7 @@
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3254,34 +3255,34 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2328
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">232
 </t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -3296,13 +3297,13 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3338,7 +3339,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8562
+          <t xml:space="preserve">89562
 </t>
         </is>
       </c>
@@ -3385,58 +3386,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19446
+          <t xml:space="preserve">1944
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3447,23 +3441,22 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n"/>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9312
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1210
@@ -3472,7 +3465,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
@@ -3484,7 +3477,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">3602
 </t>
         </is>
       </c>
@@ -3502,19 +3495,19 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">0949278
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3534,7 +3527,7 @@
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -3546,13 +3539,13 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -3564,20 +3557,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10589
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -3587,16 +3579,16 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 312
+          <t xml:space="preserve">5812
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3608,19 +3600,19 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">28239
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
@@ -3632,7 +3624,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2817
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -3662,11 +3654,15 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3677,56 +3673,50 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3756,8 +3746,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3768,25 +3757,25 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1678
+          <t xml:space="preserve">8713
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3806,7 +3795,7 @@
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2986
 </t>
         </is>
       </c>
@@ -3830,7 +3819,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3848,37 +3837,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 91
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3890,18 +3874,19 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
@@ -3948,12 +3933,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">273
@@ -3962,7 +3942,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -3980,7 +3960,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -3992,13 +3972,13 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4010,19 +3990,19 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">8118
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4034,13 +4014,13 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -4058,13 +4038,13 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -4077,7 +4057,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4097,13 +4077,13 @@
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4115,7 +4095,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4127,7 +4107,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -4139,37 +4119,36 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">12724
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4187,7 +4166,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2740
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
@@ -4199,32 +4178,31 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="Z28" s="2" t="n"/>
@@ -4261,7 +4239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4273,7 +4251,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4297,19 +4275,14 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>407</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4332,7 +4305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4356,7 +4329,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4368,7 +4341,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4385,27 +4358,22 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19484
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -4435,44 +4403,43 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9207
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
@@ -4484,37 +4451,36 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10881
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11841
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -4534,19 +4500,19 @@
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -4577,7 +4543,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -4589,7 +4555,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4601,7 +4567,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4613,7 +4579,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -4625,13 +4591,13 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">641
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -4655,7 +4621,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -4672,11 +4638,10 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4687,7 +4652,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -4699,19 +4664,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4723,25 +4688,20 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
@@ -4759,7 +4719,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4771,13 +4731,13 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -4795,7 +4755,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4813,21 +4773,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4851,7 +4805,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4869,28 +4823,23 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">9198
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -4905,7 +4854,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -4917,7 +4866,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4929,13 +4878,13 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4947,7 +4896,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -4964,12 +4913,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">321
@@ -4978,7 +4922,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -5008,13 +4952,13 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5026,19 +4970,19 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1919
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5050,7 +4994,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5068,13 +5012,13 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5098,7 +5042,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5118,19 +5062,20 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -5141,7 +5086,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5165,19 +5110,19 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5208,7 +5153,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
@@ -5220,7 +5165,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -5238,7 +5183,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5255,17 +5200,16 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5276,7 +5220,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5288,13 +5232,13 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5310,25 +5254,24 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1212
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4706
-</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">312
@@ -5337,7 +5280,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -5349,7 +5292,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5373,13 +5316,13 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -5399,13 +5342,13 @@
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11615
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -5417,61 +5360,61 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8180
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0117
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">9499
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7210
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9506
+          <t xml:space="preserve">9502
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5483,13 +5426,13 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">12304
 </t>
         </is>
       </c>
@@ -5501,13 +5444,13 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5519,13 +5462,13 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36722
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5542,7 +5485,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">123
@@ -5557,19 +5500,19 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25246
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5581,32 +5524,31 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -5630,7 +5572,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -5648,7 +5590,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -5666,7 +5608,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5692,31 +5634,31 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5728,26 +5670,26 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">7960
 </t>
         </is>
       </c>
@@ -5765,7 +5707,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -5777,19 +5719,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -5801,7 +5743,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5834,7 +5776,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5846,7 +5788,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5858,13 +5800,13 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -5882,7 +5824,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5118
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -5900,25 +5842,25 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2822
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -5936,13 +5878,13 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5965,37 +5907,37 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">179 0
+</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">29
@@ -6004,7 +5946,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -6016,7 +5958,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2049
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -6024,16 +5966,11 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">992
+</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">24
@@ -6054,7 +5991,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6066,8 +6003,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -6078,7 +6014,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
@@ -6101,7 +6037,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">324
@@ -6110,25 +6046,25 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6140,7 +6076,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6152,22 +6088,17 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1984
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19502
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -6194,14 +6125,19 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="n"/>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 14
+</t>
+        </is>
+      </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6319,13 +6255,13 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6337,25 +6273,23 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>056</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1411
 </t>
         </is>
       </c>
@@ -6367,13 +6301,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -6398,37 +6331,37 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5097
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9663
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02712
+          <t xml:space="preserve">2212
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6466,7 +6399,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6484,20 +6417,25 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6509,7 +6447,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6553,13 +6491,13 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111011
+          <t xml:space="preserve">872085
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -687,12 +687,13 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -716,13 +717,14 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -733,7 +735,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -758,15 +760,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -778,19 +775,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -802,33 +799,34 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -861,19 +859,19 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2439
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -891,7 +889,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -913,7 +911,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">322
@@ -922,13 +920,13 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
@@ -952,7 +950,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -976,19 +974,19 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">9212
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1012,13 +1010,13 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">3906
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1030,7 +1028,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1042,11 +1040,16 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="n"/>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1059,10 +1062,10 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">2305
 </t>
         </is>
       </c>
@@ -1074,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -1086,7 +1089,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1798
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1104,7 +1107,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1116,14 +1119,14 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1135,7 +1138,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4201
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -1153,7 +1156,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1177,17 +1180,22 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">742
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="n"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1200,12 +1208,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1220,8 +1223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1238,7 +1240,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1269,13 +1271,13 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">7912
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1299,7 +1301,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
@@ -1311,7 +1313,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1329,13 +1331,13 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -1354,14 +1356,13 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">1479
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1372,14 +1373,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1390,37 +1390,38 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">39726
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t xml:space="preserve">4512
+</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1437,13 +1438,13 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -1473,17 +1474,21 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3826
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="Z9" s="2" t="n"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1496,12 +1501,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1522,13 +1522,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1540,13 +1540,13 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1564,19 +1564,20 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1599,7 +1600,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1629,13 +1630,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1654,7 +1655,7 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -1666,61 +1667,51 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916
+</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1732,7 +1723,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1744,8 +1735,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1756,13 +1746,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -1772,12 +1761,7 @@
 </t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
+      <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1791,12 +1775,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -1817,19 +1796,19 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">9 841
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1841,13 +1820,13 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1857,12 +1836,7 @@
 </t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
+      <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">902
@@ -1871,13 +1845,13 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1895,13 +1869,13 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -1913,25 +1887,25 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -1947,7 +1921,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1956,7 +1930,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1968,7 +1942,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
@@ -1986,7 +1960,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1998,25 +1972,20 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2052,7 +2021,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -2076,13 +2045,13 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2098,7 +2067,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2125,7 +2099,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2137,13 +2111,13 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2155,11 +2129,16 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -2186,13 +2165,13 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
@@ -2204,7 +2183,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -2222,7 +2201,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7172
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -2244,15 +2223,10 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -2264,7 +2238,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2935
 </t>
         </is>
       </c>
@@ -2276,13 +2250,13 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">0179
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -2294,8 +2268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2312,19 +2285,19 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2342,7 +2315,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2360,7 +2333,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -2384,7 +2357,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -2403,54 +2376,49 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19404
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1123
+</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -2462,31 +2430,31 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532
+          <t xml:space="preserve">8532
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11273
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -2498,36 +2466,45 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182
-</t>
+          <t>382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9848
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="n"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100646
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="n"/>
+          <t xml:space="preserve">9708
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2543,25 +2520,24 @@
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -2579,27 +2555,32 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -2611,7 +2592,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2623,25 +2604,25 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2659,11 +2640,16 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="Z17" s="2" t="n"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2679,49 +2665,45 @@
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2736,22 +2718,27 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0 2
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>892</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2768,13 +2755,13 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">542
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2792,17 +2779,21 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="Z18" s="2" t="n"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2817,13 +2808,13 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -2835,7 +2826,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2847,12 +2838,13 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2876,11 +2868,16 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -2919,7 +2916,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2931,7 +2928,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2943,11 +2940,16 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="Z19" s="2" t="n"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2960,16 +2962,21 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2981,7 +2988,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">0596
 </t>
         </is>
       </c>
@@ -3005,31 +3012,26 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
@@ -3053,13 +3055,13 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -3071,7 +3073,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3083,7 +3085,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
@@ -3093,7 +3095,11 @@
 </t>
         </is>
       </c>
-      <c r="Z20" s="2" t="n"/>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3106,10 +3112,16 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3120,7 +3132,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3132,7 +3144,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3150,7 +3162,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3181,13 +3193,13 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3199,36 +3211,46 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="X21" s="2" t="n"/>
       <c r="Y21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">903
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3241,21 +3263,27 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3279,7 +3307,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3291,25 +3319,25 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">9912
 </t>
         </is>
       </c>
@@ -3321,13 +3349,13 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3339,7 +3367,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89562
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -3351,29 +3379,34 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">947
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="n"/>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3389,7 +3422,7 @@
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19426
 </t>
         </is>
       </c>
@@ -3401,36 +3434,37 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3441,19 +3475,20 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">19529
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t xml:space="preserve">9512
+</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
@@ -3465,53 +3500,58 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3602
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">377
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0949278
+          <t xml:space="preserve">1987
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="n"/>
+          <t xml:space="preserve">94256
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3524,7 +3564,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">285
@@ -3557,38 +3602,48 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5812
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3600,19 +3655,19 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -3624,7 +3679,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">8217
 </t>
         </is>
       </c>
@@ -3634,14 +3689,24 @@
 </t>
         </is>
       </c>
-      <c r="X24" s="2" t="n"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="Z24" s="2" t="n"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3654,88 +3719,91 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4441</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3746,12 +3814,13 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -3763,23 +3832,22 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8713
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="n"/>
+          <t xml:space="preserve">693
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3792,16 +3860,21 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2986
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -3813,7 +3886,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -3837,26 +3910,31 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19896
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -3874,13 +3952,13 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3898,29 +3976,34 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="n"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -3954,7 +4037,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -3966,19 +4049,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -3990,19 +4073,19 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">9222
 </t>
         </is>
       </c>
@@ -4014,13 +4097,13 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4038,30 +4121,40 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="W27" s="2" t="n"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="n"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -4077,13 +4170,13 @@
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">2327
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4095,7 +4188,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4119,60 +4212,61 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12724
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">402
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4184,28 +4278,34 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>856</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="n"/>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4233,31 +4333,31 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4273,21 +4373,22 @@
 </t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4305,7 +4406,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4323,29 +4424,34 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="n"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -4361,25 +4467,25 @@
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">14984
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1896
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4397,32 +4503,32 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">2925
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">961
+          <t xml:space="preserve">3921
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4439,7 +4545,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4463,28 +4569,33 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t xml:space="preserve">3122
+</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="Z30" s="2" t="n"/>
+          <t xml:space="preserve">524
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4506,7 +4617,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4518,13 +4629,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4536,14 +4647,14 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4555,7 +4666,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -4573,25 +4684,25 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">641
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -4603,29 +4714,34 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">773
+          <t xml:space="preserve">7478
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="n"/>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4638,22 +4754,26 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">12328
+</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4664,19 +4784,18 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4686,35 +4805,34 @@
 </t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -4731,7 +4849,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -4743,7 +4861,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4755,11 +4873,15 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="n"/>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4773,10 +4895,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">926
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4823,20 +4951,20 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4854,7 +4982,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4866,41 +4994,46 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">803
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">803
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="n"/>
       <c r="AA33" t="inlineStr">
         <is>
           <t>22</t>
@@ -4922,13 +5055,13 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -4940,7 +5073,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -4958,7 +5091,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4970,7 +5103,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4982,19 +5115,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5012,13 +5145,13 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5042,11 +5175,16 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="n"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -5059,7 +5197,12 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -5110,23 +5253,28 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -5135,7 +5283,7 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5153,7 +5301,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -5187,7 +5335,12 @@
 </t>
         </is>
       </c>
-      <c r="Z35" s="2" t="n"/>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5200,16 +5353,17 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">9336
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5238,7 +5392,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5250,25 +5404,31 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5280,7 +5440,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2350
 </t>
         </is>
       </c>
@@ -5292,13 +5452,13 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -5316,7 +5476,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -5326,7 +5486,12 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="2" t="n"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5348,7 +5513,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">19295
 </t>
         </is>
       </c>
@@ -5360,14 +5525,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -5378,7 +5542,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5390,31 +5554,31 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">9511
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9502
+          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5426,43 +5590,43 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12304
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">73672
 </t>
         </is>
       </c>
@@ -5472,7 +5636,12 @@
 </t>
         </is>
       </c>
-      <c r="Z37" s="2" t="n"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2473
+</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5485,7 +5654,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">123
@@ -5500,7 +5669,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5524,31 +5693,32 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
@@ -5566,53 +5736,58 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">7235
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">149
 </t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="n"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5628,37 +5803,35 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5670,26 +5843,26 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1490
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
@@ -5707,48 +5880,57 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="n"/>
-      <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5761,7 +5943,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">325
@@ -5776,7 +5963,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5788,7 +5975,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5800,13 +5987,13 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5818,13 +6005,13 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5842,13 +6029,13 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2822
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5860,22 +6047,22 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -5884,7 +6071,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5894,7 +6081,12 @@
 </t>
         </is>
       </c>
-      <c r="Z40" s="2" t="n"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8262
+</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>27</t>
@@ -5907,16 +6099,16 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179 0
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5934,14 +6126,13 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5952,28 +6143,38 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2091
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -5991,30 +6192,31 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6024,7 +6226,12 @@
 </t>
         </is>
       </c>
-      <c r="Z41" s="2" t="n"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6038,33 +6245,28 @@
         </is>
       </c>
       <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">324
 </t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6076,73 +6278,88 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1728
+</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">86
 </t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 14
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="n"/>
-      <c r="W42" s="2" t="n"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="X42" s="2" t="n"/>
       <c r="Y42" s="2" t="n"/>
       <c r="Z42" s="2" t="n"/>
@@ -6255,58 +6472,55 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>056</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">23662
 </t>
         </is>
       </c>
@@ -6316,10 +6530,15 @@
 </t>
         </is>
       </c>
-      <c r="Q45" s="2" t="n"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1069
+</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">1027
 </t>
         </is>
       </c>
@@ -6331,19 +6550,19 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">8927
 </t>
         </is>
       </c>
@@ -6355,17 +6574,22 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
+          <t xml:space="preserve">193272
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6381,28 +6605,28 @@
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
 </t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -6411,37 +6635,37 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6453,55 +6677,65 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">229
 </t>
         </is>
       </c>
-      <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">602
 </t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">823
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872085
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="n"/>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 9929
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
@@ -627,122 +627,102 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="2" t="n"/>
@@ -763,140 +743,117 @@
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -914,140 +871,117 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1065,135 +999,113 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1211,14 +1123,12 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1228,117 +1138,98 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1356,8 +1247,7 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1367,14 +1257,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1384,92 +1272,77 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39726
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
-</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
-</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>488</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1479,14 +1352,12 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
-</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,140 +1375,117 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,33 +1503,28 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1693,44 +1536,37 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1740,8 +1576,7 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1751,14 +1586,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y11" s="2" t="n"/>
@@ -1778,135 +1611,113 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 841
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">086
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,135 +1735,113 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,146 +1858,122 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2226,44 +1991,37 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2935
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2273,92 +2031,77 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2376,20 +2119,17 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2399,69 +2139,58 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2471,38 +2200,32 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9708
-</t>
+          <t>088</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2517,17 +2240,19 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2537,117 +2262,98 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2685,20 +2391,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2708,32 +2411,27 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 2
-</t>
+          <t>0 2</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2743,38 +2441,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">542
-</t>
+          <t>542</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -2784,14 +2476,12 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2808,146 +2498,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2964,135 +2630,113 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0596
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -3114,141 +2758,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3265,146 +2890,122 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3422,20 +3023,17 @@
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19426
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3445,111 +3043,93 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>838</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19529
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9512
-</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
-</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1987
-</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94256
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3566,44 +3146,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3613,98 +3186,82 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
-</t>
+          <t>99919991</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3722,20 +3279,17 @@
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3745,14 +3299,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3762,38 +3314,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3808,26 +3354,22 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3837,14 +3379,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">693
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -3862,146 +3402,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19896
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4019,140 +3535,117 @@
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4170,140 +3663,117 @@
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>402</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4321,135 +3791,113 @@
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4467,44 +3915,37 @@
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14984
-</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>588</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4514,81 +3955,68 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3921
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3122
-</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4611,135 +4039,113 @@
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7478
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4756,14 +4162,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12328
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4778,14 +4182,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4795,39 +4197,33 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4837,38 +4233,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>358</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
@@ -4878,8 +4268,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="Z32" s="2" t="n"/>
@@ -4897,141 +4286,118 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5046,143 +4412,124 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5199,146 +4546,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5356,140 +4679,117 @@
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9336
-</t>
+          <t>936</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5507,26 +4807,22 @@
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
-</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19295
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5536,110 +4832,92 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9499
-</t>
+          <t>491</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9511
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1502
-</t>
+          <t>502</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
-</t>
+          <t>703</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
-</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73672
-</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2473
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5657,135 +4935,117 @@
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5803,8 +5063,7 @@
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -5814,8 +5073,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5825,93 +5083,78 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241 7</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
@@ -5921,14 +5164,12 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5945,146 +5186,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
-</t>
+          <t>472</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8262
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6102,32 +5319,27 @@
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -6137,99 +5349,83 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6248,116 +5444,97 @@
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="X42" s="2" t="n"/>
@@ -6377,8 +5554,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D43" s="2" t="n"/>
@@ -6418,8 +5594,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -6460,26 +5635,22 @@
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -6489,105 +5660,88 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23662
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
-</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2412
-</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
-</t>
+          <t>387</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8927
-</t>
+          <t>857</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193272
-</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6605,135 +5759,113 @@
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 9929
-</t>
+          <t>0 22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>128</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>196</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2 81</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 1 01</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>815</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>173</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>412</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2277,23 +2277,23 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>221</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>101</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>289</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>219</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -3023,7 +3023,7 @@
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
@@ -3094,17 +3094,17 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>347</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>99919991</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>856</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>293</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>000</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>278</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3960,13 +3960,13 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>921</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>451</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>876</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>903</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>482</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>262</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>803</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>286</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>254</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4679,7 +4679,7 @@
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>86</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>442</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4852,22 +4852,22 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4935,7 +4935,7 @@
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>186</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5108,13 +5108,13 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>241 7</t>
+          <t>241 0</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>298</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>196</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>269</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5489,52 +5489,52 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X42" s="2" t="n"/>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>963</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5759,7 +5759,7 @@
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>99</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -5809,42 +5809,42 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>223</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5862,10 +5862,14 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>2 1</t>
+        </is>
+      </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>0 22</t>
+          <t>00 2989</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/508/Top_Excel_with_OCR_Results.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>104</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1662,17 +1662,17 @@
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>905</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>67</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0 1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>919</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>353</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>109</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>114</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2543,22 +2543,22 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0 01</t>
+          <t>0 0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>88</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3023,7 +3023,7 @@
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>577</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>812</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>673</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -3402,67 +3402,67 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>918</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3477,17 +3477,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>08</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>63</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3960,13 +3960,13 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>263</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>803</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4367,17 +4367,17 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>78</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>290</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4464,17 +4464,17 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>09</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -4724,17 +4724,17 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>155</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4852,17 +4852,17 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4970,37 +4970,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>886</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5114,7 +5114,7 @@
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>95</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5236,17 +5236,17 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>869</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="2" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5675,18 +5675,18 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>311</t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>241</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>327</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5784,42 +5784,42 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5862,14 +5862,10 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>2 1</t>
-        </is>
-      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>00 2989</t>
+          <t>0 2989</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
